--- a/resources/membersalums_REF_ONLY.xlsx
+++ b/resources/membersalums_REF_ONLY.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\e-steam.github.io\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71667BA7-F6A6-414D-8EB0-FA7A6702D697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B982F1DD-6517-4B6F-9666-02E0D9B1F1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="16950" windowHeight="15585" activeTab="1" xr2:uid="{FDA1AC23-9684-4951-B0B2-FF55B1E34EAF}"/>
+    <workbookView xWindow="31020" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{FDA1AC23-9684-4951-B0B2-FF55B1E34EAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="64">
   <si>
     <t>Name</t>
   </si>
@@ -75,9 +75,6 @@
     <t>https://www.autumdowney.com/</t>
   </si>
   <si>
-    <t>PhD in Geomicrobiology (Earth &amp; Space Sciences)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dr. Samantha Garza </t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>Erendira</t>
   </si>
   <si>
-    <t>Maya Harari</t>
-  </si>
-  <si>
     <t>Dr. Steven Stetzler</t>
   </si>
   <si>
@@ -147,27 +141,18 @@
     <t>Astrobiology Program Administrator, Astronomy Department Administrative Specialist</t>
   </si>
   <si>
-    <t>PhD Student in Physics</t>
-  </si>
-  <si>
     <t>https://stevenstetzler.com/</t>
   </si>
   <si>
     <t>https://www.tomwagg.com/</t>
   </si>
   <si>
-    <t>Contact to confirm</t>
-  </si>
-  <si>
     <t>Anna Grace Ulses</t>
   </si>
   <si>
     <t>Hector Emanuel Delgado Diaz</t>
   </si>
   <si>
-    <t>Pip Samuel Peterse</t>
-  </si>
-  <si>
     <t>Ula Jones</t>
   </si>
   <si>
@@ -205,6 +190,45 @@
   </si>
   <si>
     <t>resources/volunteers/pete.png</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/maya-gatt-harari-0819521b3/</t>
+  </si>
+  <si>
+    <t>Maya Gatt Harari</t>
+  </si>
+  <si>
+    <t>resources/volunteers/maya.jpg</t>
+  </si>
+  <si>
+    <t>PhD Student in Biomechanical Engineering</t>
+  </si>
+  <si>
+    <t>Pip Petersen</t>
+  </si>
+  <si>
+    <t>resources/volunteers/pip.jpg</t>
+  </si>
+  <si>
+    <t>https://smandersen.reclaim.hosting</t>
+  </si>
+  <si>
+    <t>resources/volunteers/sydney.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Natalie Paquette</t>
+  </si>
+  <si>
+    <t>Physics Department Faculty</t>
+  </si>
+  <si>
+    <t>resources/volunteers/natalie/jpeg</t>
+  </si>
+  <si>
+    <t>resources/volunteers/tomwagg.jpg</t>
+  </si>
+  <si>
+    <t>PhD in Geomicrobiology (Earth and Space Sciences)</t>
   </si>
 </sst>
 </file>
@@ -252,12 +276,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -594,14 +617,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F2436D-6078-4782-A3F2-45402429735A}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -618,166 +641,169 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
       <c r="E3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="C16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="C17" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E1CA9D-58C7-4A5A-AD88-735485644128}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
@@ -800,11 +826,11 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
@@ -817,142 +843,143 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
+      <c r="A4" t="s">
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>39</v>
+      <c r="E11" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/resources/membersalums_REF_ONLY.xlsx
+++ b/resources/membersalums_REF_ONLY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\e-steam.github.io\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B982F1DD-6517-4B6F-9666-02E0D9B1F1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BDD6F2-A8D5-48D5-8F07-3A6DAE48BD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31020" yWindow="2175" windowWidth="21600" windowHeight="11295" xr2:uid="{FDA1AC23-9684-4951-B0B2-FF55B1E34EAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDA1AC23-9684-4951-B0B2-FF55B1E34EAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
   <si>
     <t>Name</t>
   </si>
@@ -150,15 +150,9 @@
     <t>Anna Grace Ulses</t>
   </si>
   <si>
-    <t>Hector Emanuel Delgado Diaz</t>
-  </si>
-  <si>
     <t>Ula Jones</t>
   </si>
   <si>
-    <t>Natalie Paquette</t>
-  </si>
-  <si>
     <t>Cassidy Johnson</t>
   </si>
   <si>
@@ -229,16 +223,42 @@
   </si>
   <si>
     <t>PhD in Geomicrobiology (Earth and Space Sciences)</t>
+  </si>
+  <si>
+    <t>resources/volunteers/steven.png</t>
+  </si>
+  <si>
+    <t>resources/volunteers/hector.png</t>
+  </si>
+  <si>
+    <t>htohfa.github.io</t>
+  </si>
+  <si>
+    <t>resources/volunteers/hurum.jpeg</t>
+  </si>
+  <si>
+    <t>Héctor Emanuel Delgado Díaz</t>
+  </si>
+  <si>
+    <t>resources/volunteers/lainey.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -273,18 +293,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -617,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F2436D-6078-4782-A3F2-45402429735A}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -641,163 +665,167 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="D3" s="4"/>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>57</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" display="http://htohfa.github.io/" xr:uid="{FF37C9DD-E8B0-48C0-8709-0F1F9DA2E8BD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -826,7 +854,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -843,7 +871,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -854,13 +882,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -874,7 +902,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -888,7 +916,7 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -902,7 +930,7 @@
         <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -916,7 +944,7 @@
         <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -930,24 +958,24 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
         <v>51</v>
-      </c>
-      <c r="E9" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -963,7 +991,9 @@
       <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -979,7 +1009,7 @@
         <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/resources/membersalums_REF_ONLY.xlsx
+++ b/resources/membersalums_REF_ONLY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\e-steam.github.io\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BDD6F2-A8D5-48D5-8F07-3A6DAE48BD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214E4B0C-BEBD-427D-9D6A-FF886A76D234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDA1AC23-9684-4951-B0B2-FF55B1E34EAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FDA1AC23-9684-4951-B0B2-FF55B1E34EAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="69">
   <si>
     <t>Name</t>
   </si>
@@ -90,9 +90,6 @@
     <t>PhD in Earth and Space Sciences &amp; Astrobiology</t>
   </si>
   <si>
-    <t>Samantha Gilbert-Janizek</t>
-  </si>
-  <si>
     <t>PhD Student in Astronomy &amp; Astrobiology</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>they/them</t>
   </si>
   <si>
-    <t>Erendira</t>
-  </si>
-  <si>
     <t>Dr. Steven Stetzler</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
     <t>Physics Department Faculty</t>
   </si>
   <si>
-    <t>resources/volunteers/natalie/jpeg</t>
-  </si>
-  <si>
     <t>resources/volunteers/tomwagg.jpg</t>
   </si>
   <si>
@@ -241,6 +232,18 @@
   </si>
   <si>
     <t>resources/volunteers/lainey.jpg</t>
+  </si>
+  <si>
+    <t>Undergraduate Student in Astronomy</t>
+  </si>
+  <si>
+    <t>resources/volunteers/cassidy.jpg</t>
+  </si>
+  <si>
+    <t>resources/volunteers/natalie.jpeg</t>
+  </si>
+  <si>
+    <t>Dr. Samantha Gilbert-Janizek</t>
   </si>
 </sst>
 </file>
@@ -297,14 +300,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -641,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30F2436D-6078-4782-A3F2-45402429735A}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -665,160 +667,140 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
         <v>28</v>
       </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -831,7 +813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22E1CA9D-58C7-4A5A-AD88-735485644128}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
@@ -854,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -871,7 +853,7 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -882,13 +864,13 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -902,7 +884,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -916,71 +898,71 @@
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
         <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -989,15 +971,15 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>62</v>
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
@@ -1006,10 +988,27 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
